--- a/CUADRO_DatosTiempos.xlsx
+++ b/CUADRO_DatosTiempos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\TRABAJO_FINAL_PA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D58437FE-6F8E-4037-A51A-2CD1EA443DB2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1A84991-9D03-416E-A4D7-73972CFFA29F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{E5BC5622-309B-4FD6-B361-838C0A04C342}"/>
   </bookViews>

--- a/CUADRO_DatosTiempos.xlsx
+++ b/CUADRO_DatosTiempos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\TRABAJO_FINAL_PA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1A84991-9D03-416E-A4D7-73972CFFA29F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29E8356D-261F-47CB-B3F2-87DBB428255C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{E5BC5622-309B-4FD6-B361-838C0A04C342}"/>
   </bookViews>

--- a/CUADRO_DatosTiempos.xlsx
+++ b/CUADRO_DatosTiempos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\TRABAJO_FINAL_PA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29E8356D-261F-47CB-B3F2-87DBB428255C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EC4A4B0-BC5A-4FCE-BDA9-09038FC0F76A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{E5BC5622-309B-4FD6-B361-838C0A04C342}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>Shellsort</t>
   </si>
@@ -39,9 +39,6 @@
     <t>Quicksort</t>
   </si>
   <si>
-    <t>…</t>
-  </si>
-  <si>
     <t>tiempo 1</t>
   </si>
   <si>
@@ -57,43 +54,10 @@
     <t>Sumatoria</t>
   </si>
   <si>
-    <t>0.0000842 s</t>
-  </si>
-  <si>
-    <t>0.0000355 s</t>
-  </si>
-  <si>
     <t>Promedio total</t>
   </si>
   <si>
-    <t>0.0007541 s</t>
-  </si>
-  <si>
-    <t>0.0006615 s</t>
-  </si>
-  <si>
-    <t>0.0008616 s</t>
-  </si>
-  <si>
-    <t>0.0007344 s</t>
-  </si>
-  <si>
-    <t>0.0017603 s</t>
-  </si>
-  <si>
-    <t>0.0012029 s</t>
-  </si>
-  <si>
-    <t>0.0035201 s</t>
-  </si>
-  <si>
-    <t>0.0025373 s</t>
-  </si>
-  <si>
-    <t>0.000880025 s</t>
-  </si>
-  <si>
-    <t>0.000634325 s</t>
+    <t>valores en segundos (s)</t>
   </si>
 </sst>
 </file>
@@ -152,7 +116,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{80690229-893E-4C54-8066-D33B21120BA1}" name="Tabla1" displayName="Tabla1" ref="A1:C7" totalsRowShown="0">
   <autoFilter ref="A1:C7" xr:uid="{CF2D7E38-7DFB-47DC-BC79-DF8D360D3C48}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{B67111AD-D1F4-434A-9C18-50F9D48C1CB6}" name="…"/>
+    <tableColumn id="1" xr3:uid="{B67111AD-D1F4-434A-9C18-50F9D48C1CB6}" name="valores en segundos (s)"/>
     <tableColumn id="2" xr3:uid="{F6D75F8F-915D-4EB2-8154-46808D64937A}" name="Shellsort"/>
     <tableColumn id="3" xr3:uid="{8BABF368-559C-4833-A9C3-06F02B768C54}" name="Quicksort"/>
   </tableColumns>
@@ -460,14 +424,14 @@
   <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.85546875" customWidth="1"/>
+    <col min="1" max="1" width="24.28515625" customWidth="1"/>
     <col min="2" max="2" width="13.5703125" customWidth="1"/>
     <col min="3" max="3" width="13.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -478,68 +442,68 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" t="s">
-        <v>9</v>
+        <v>2</v>
+      </c>
+      <c r="B2">
+        <v>8.42E-5</v>
+      </c>
+      <c r="C2">
+        <v>3.5500000000000002E-5</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" t="s">
-        <v>12</v>
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>7.5409999999999995E-4</v>
+      </c>
+      <c r="C3">
+        <v>6.6149999999999998E-4</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" t="s">
-        <v>14</v>
+        <v>4</v>
+      </c>
+      <c r="B4">
+        <v>8.6160000000000002E-4</v>
+      </c>
+      <c r="C4">
+        <v>7.3439999999999996E-4</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" t="s">
-        <v>16</v>
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>1.7603E-3</v>
+      </c>
+      <c r="C5">
+        <v>1.2029E-3</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" t="s">
-        <v>18</v>
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>3.5201E-3</v>
+      </c>
+      <c r="C6">
+        <v>2.5373000000000001E-3</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" t="s">
-        <v>20</v>
+        <v>7</v>
+      </c>
+      <c r="B7">
+        <v>8.8002499999999999E-4</v>
+      </c>
+      <c r="C7">
+        <v>6.3432500000000004E-4</v>
       </c>
     </row>
   </sheetData>

--- a/CUADRO_DatosTiempos.xlsx
+++ b/CUADRO_DatosTiempos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\TRABAJO_FINAL_PA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EC4A4B0-BC5A-4FCE-BDA9-09038FC0F76A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2184C6F8-AD12-43B5-98BC-C8D64D4901B8}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{E5BC5622-309B-4FD6-B361-838C0A04C342}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="10">
   <si>
     <t>Shellsort</t>
   </si>
@@ -39,25 +39,28 @@
     <t>Quicksort</t>
   </si>
   <si>
-    <t>tiempo 1</t>
-  </si>
-  <si>
-    <t>tiempo 2</t>
-  </si>
-  <si>
-    <t>tiempo 3</t>
-  </si>
-  <si>
-    <t>tiempo 4</t>
-  </si>
-  <si>
     <t>Sumatoria</t>
   </si>
   <si>
-    <t>Promedio total</t>
-  </si>
-  <si>
-    <t>valores en segundos (s)</t>
+    <t>Promedio Total</t>
+  </si>
+  <si>
+    <t>Valores en Segundos (s)</t>
+  </si>
+  <si>
+    <t>Métodos Logarítmicos</t>
+  </si>
+  <si>
+    <t>Tiempo 1</t>
+  </si>
+  <si>
+    <t>Tiempo 2</t>
+  </si>
+  <si>
+    <t>Tiempo 3</t>
+  </si>
+  <si>
+    <t>Tiempo 4</t>
   </si>
 </sst>
 </file>
@@ -113,12 +116,24 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{80690229-893E-4C54-8066-D33B21120BA1}" name="Tabla1" displayName="Tabla1" ref="A1:C7" totalsRowShown="0">
-  <autoFilter ref="A1:C7" xr:uid="{CF2D7E38-7DFB-47DC-BC79-DF8D360D3C48}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{80690229-893E-4C54-8066-D33B21120BA1}" name="Tabla1" displayName="Tabla1" ref="A1:C5" totalsRowShown="0">
+  <autoFilter ref="A1:C5" xr:uid="{CF2D7E38-7DFB-47DC-BC79-DF8D360D3C48}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{B67111AD-D1F4-434A-9C18-50F9D48C1CB6}" name="valores en segundos (s)"/>
+    <tableColumn id="1" xr3:uid="{B67111AD-D1F4-434A-9C18-50F9D48C1CB6}" name="Valores en Segundos (s)"/>
     <tableColumn id="2" xr3:uid="{F6D75F8F-915D-4EB2-8154-46808D64937A}" name="Shellsort"/>
     <tableColumn id="3" xr3:uid="{8BABF368-559C-4833-A9C3-06F02B768C54}" name="Quicksort"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{DBA73C1C-BFCE-40E1-B364-47E77FC8194B}" name="Tabla5" displayName="Tabla5" ref="E1:G3" totalsRowShown="0">
+  <autoFilter ref="E1:G3" xr:uid="{D0FDD154-70C1-496A-84F4-7D30ABC10961}"/>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{BC0D65C5-4425-4591-83C3-C6C2CAF4359C}" name="Métodos Logarítmicos"/>
+    <tableColumn id="2" xr3:uid="{D94CFD16-4382-47BF-8059-1A8E836DE8D6}" name="Sumatoria"/>
+    <tableColumn id="3" xr3:uid="{99856CAA-5264-4F71-8B64-879CBC5440E6}" name="Promedio Total"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -421,17 +436,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BEDB89D-33B7-423D-8ED4-E5BF76AC7878}">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.28515625" customWidth="1"/>
     <col min="2" max="2" width="13.5703125" customWidth="1"/>
     <col min="3" max="3" width="13.42578125" customWidth="1"/>
+    <col min="5" max="5" width="24.28515625" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="7" max="7" width="18.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -439,10 +457,19 @@
       <c r="C1" t="s">
         <v>1</v>
       </c>
+      <c r="E1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B2">
         <v>8.42E-5</v>
@@ -450,10 +477,19 @@
       <c r="C2">
         <v>3.5500000000000002E-5</v>
       </c>
+      <c r="E2" t="s">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>3.5201E-3</v>
+      </c>
+      <c r="G2">
+        <v>8.8002499999999999E-4</v>
+      </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>7.5409999999999995E-4</v>
@@ -461,10 +497,19 @@
       <c r="C3">
         <v>6.6149999999999998E-4</v>
       </c>
+      <c r="E3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>2.5373000000000001E-3</v>
+      </c>
+      <c r="G3">
+        <v>6.3432500000000004E-4</v>
+      </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B4">
         <v>8.6160000000000002E-4</v>
@@ -473,43 +518,23 @@
         <v>7.3439999999999996E-4</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B5">
         <v>1.7603E-3</v>
       </c>
       <c r="C5">
         <v>1.2029E-3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>3.5201E-3</v>
-      </c>
-      <c r="C6">
-        <v>2.5373000000000001E-3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7">
-        <v>8.8002499999999999E-4</v>
-      </c>
-      <c r="C7">
-        <v>6.3432500000000004E-4</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="4294967293" r:id="rId1"/>
+  <tableParts count="2">
+    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
   </tableParts>
 </worksheet>
 </file>
--- a/CUADRO_DatosTiempos.xlsx
+++ b/CUADRO_DatosTiempos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\TRABAJO_FINAL_PA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2184C6F8-AD12-43B5-98BC-C8D64D4901B8}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4C8A715-64BF-46C7-9F93-4C39B7A6B635}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{E5BC5622-309B-4FD6-B361-838C0A04C342}"/>
   </bookViews>
